--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>69.60248626761044</v>
+        <v>11.3104040184867</v>
       </c>
       <c r="D2" t="n">
-        <v>69.41010990277523</v>
+        <v>11.27914285920098</v>
       </c>
       <c r="E2" t="n">
-        <v>13.51801160743139</v>
+        <v>2.196676886207602</v>
       </c>
       <c r="F2" t="n">
-        <v>13.74467940236956</v>
+        <v>2.233510402885053</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.52532636754273</v>
+        <v>7.397865534725694</v>
       </c>
       <c r="D3" t="n">
-        <v>45.40540552670237</v>
+        <v>7.378378398089135</v>
       </c>
       <c r="E3" t="n">
-        <v>13.51801160743139</v>
+        <v>2.196676886207602</v>
       </c>
       <c r="F3" t="n">
-        <v>13.74467940236956</v>
+        <v>2.233510402885053</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.87805737617066</v>
+        <v>6.155184323627732</v>
       </c>
       <c r="D4" t="n">
-        <v>36.96384470143188</v>
+        <v>6.006624763982681</v>
       </c>
       <c r="E4" t="n">
-        <v>13.51801160743139</v>
+        <v>2.196676886207602</v>
       </c>
       <c r="F4" t="n">
-        <v>13.74467940236956</v>
+        <v>2.233510402885053</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
